--- a/data/administracion_de_tribunales/OP_LEY148FinalEmitidas.xlsx
+++ b/data/administracion_de_tribunales/OP_LEY148FinalEmitidas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\administracion_de_tribunales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6570534-C6C0-451D-98F1-C40814F22017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{165009D7-53CD-4819-9DFB-30827804FE2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" tabRatio="748" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13056" tabRatio="748" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2020-2021" sheetId="4" r:id="rId1"/>
@@ -155,12 +155,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1515,24 +1518,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3794E50D-B6C2-4A62-B0A4-A823E09C29A8}">
   <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="3" width="8.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1544,13 +1550,13 @@
         <v>8</v>
       </c>
       <c r="C2" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F2" s="3">
         <v>0</v>
@@ -1561,16 +1567,16 @@
         <v>7</v>
       </c>
       <c r="B3" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C3" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3" s="3">
         <v>0</v>
@@ -1581,19 +1587,19 @@
         <v>8</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D4" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F4" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1601,16 +1607,16 @@
         <v>9</v>
       </c>
       <c r="B5" s="3">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E5" s="3">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
@@ -1621,16 +1627,16 @@
         <v>10</v>
       </c>
       <c r="B6" s="3">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C6" s="3">
         <v>3</v>
       </c>
       <c r="D6" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E6" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F6" s="3">
         <v>0</v>
@@ -1641,16 +1647,16 @@
         <v>11</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3">
         <v>9</v>
       </c>
       <c r="D7" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E7" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F7" s="3">
         <v>1</v>
@@ -1661,16 +1667,16 @@
         <v>12</v>
       </c>
       <c r="B8" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C8" s="3">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="3">
         <v>0</v>
@@ -1681,16 +1687,16 @@
         <v>13</v>
       </c>
       <c r="B9" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" s="3">
         <v>3</v>
       </c>
       <c r="E9" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F9" s="3">
         <v>0</v>
@@ -1701,19 +1707,19 @@
         <v>14</v>
       </c>
       <c r="B10" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C10" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F10" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -1721,16 +1727,16 @@
         <v>15</v>
       </c>
       <c r="B11" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C11" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D11" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E11" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F11" s="3">
         <v>0</v>
@@ -1741,19 +1747,19 @@
         <v>16</v>
       </c>
       <c r="B12" s="3">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C12" s="3">
         <v>5</v>
       </c>
       <c r="D12" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="3">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="F12" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -1761,19 +1767,19 @@
         <v>17</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C13" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E13" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F13" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -1781,16 +1787,16 @@
         <v>18</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D14" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E14" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F14" s="3">
         <v>0</v>
@@ -1802,23 +1808,23 @@
       </c>
       <c r="B15" s="3">
         <f>SUM(B2:B14)</f>
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="C15" s="3">
         <f t="shared" ref="C15:F15" si="0">SUM(C2:C14)</f>
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="D15" s="3">
         <f t="shared" si="0"/>
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="E15" s="3">
         <f t="shared" si="0"/>
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="F15" s="3">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
